--- a/03-BOM/BillofMaterials.xlsx
+++ b/03-BOM/BillofMaterials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtfr5\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D44632F5-2345-49CF-9713-1D9CDF556E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587EB93D-9A76-4667-9B13-BE1BE4F4E256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
   <si>
     <t>Bill of Materials Example</t>
   </si>
@@ -92,61 +92,27 @@
     <t>74HC165-Q100</t>
   </si>
   <si>
-    <t>https://www.mouser.com/ProductDetail/Nexperia/74HC165D-Q100118?qs=sGAEpiMZZMutXGli8Ay4kD1Rik6g2cV%252B%252BQvCmhxAH0s%3D</t>
-  </si>
-  <si>
     <t>Nexperia</t>
   </si>
   <si>
     <t>https://assets.nexperia.com/documents/data-sheet/74HC_HCT165_Q100.pdf</t>
   </si>
   <si>
-    <t>Mouser</t>
-  </si>
-  <si>
-    <t>771-74HC165D-Q100</t>
-  </si>
-  <si>
     <t>Voltage Regulator</t>
   </si>
   <si>
     <t>Pushbutton Switch</t>
   </si>
   <si>
-    <t>611-PTS645SL502</t>
-  </si>
-  <si>
     <t>PTS645SL50-2 LFS</t>
   </si>
   <si>
     <t>C&amp;K</t>
   </si>
   <si>
-    <t>785-1438-5-ND</t>
-  </si>
-  <si>
     <t>DigiKey</t>
   </si>
   <si>
-    <t>Alpha &amp; Omega Sumiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	
-AOT2618L</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/alpha-omega-semiconductor-inc/AOT2618L/3603378</t>
-  </si>
-  <si>
-    <t>https://www.aosmd.com/res/datasheets/AOT2618L.pdf</t>
-  </si>
-  <si>
-    <t>https://www.mouser.com/ProductDetail/CK/PTS645SL50-2-LFS?qs=rqnA19JZHeTZYaJU%252B5olWA%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.ck-components.com/media/1471/pts645.pdf</t>
-  </si>
-  <si>
     <t>PIC Curiosity Nano Dev Kit</t>
   </si>
   <si>
@@ -192,9 +158,6 @@
     <t>OptiFuse</t>
   </si>
   <si>
-    <t>2298-TSA-1.2A-ND</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/optifuse/TSA-1-2A/12089530</t>
   </si>
   <si>
@@ -223,6 +186,47 @@
   </si>
   <si>
     <t>283-BK4-4004-1-R-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/nexperia-usa-inc/74HC165D-653/763013</t>
+  </si>
+  <si>
+    <t>LM7805</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="19"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://www.digikey.com/en/products/detail/stmicroelectronics/L7805CV/585964</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.st.com/content/ccc/resource/technical/document/datasheet/41/4f/b3/b0/12/d4/47/88/CD00000444.pdf/files/CD00000444.pdf/jcr:content/translations/en.CD00000444.pdf</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/c-k/Y97HT21A1EAFP/1146755</t>
+  </si>
+  <si>
+    <t>https://www.ckswitches.com/media/1471/pts645.pdf</t>
+  </si>
+  <si>
+    <t>497-1443-5-ND</t>
+  </si>
+  <si>
+    <t>1727-2788-1-ND</t>
+  </si>
+  <si>
+    <t>CKN9098-ND</t>
+  </si>
+  <si>
+    <t>283-2619-ND</t>
   </si>
 </sst>
 </file>
@@ -232,7 +236,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -270,13 +274,25 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="19"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color rgb="FF444444"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <color indexed="8"/>
+      <name val="Garamond"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Garamond"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -295,8 +311,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -332,12 +354,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -358,10 +421,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -722,32 +796,32 @@
   <sheetData>
     <row r="1" spans="2:15" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:15" ht="30" x14ac:dyDescent="0.4">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
     </row>
     <row r="3" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>2</v>
@@ -779,29 +853,29 @@
         <v>3</v>
       </c>
       <c r="D4" s="6">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="E4" s="6">
         <f t="shared" ref="E4:E11" si="0">C4*D4</f>
-        <v>0.72</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>59</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>9</v>
@@ -809,7 +883,7 @@
     </row>
     <row r="5" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
@@ -836,12 +910,12 @@
         <v>13</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="15" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5">
         <v>16</v>
@@ -868,84 +942,84 @@
         <v>16</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="5">
         <v>2</v>
       </c>
       <c r="D7" s="6">
-        <v>1.66</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="6">
         <f t="shared" si="0"/>
-        <v>3.32</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="5">
         <v>16</v>
       </c>
       <c r="D8" s="6">
-        <v>0.28000000000000003</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
-        <v>4.4800000000000004</v>
+        <v>3.2959999999999998</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>26</v>
+        <v>57</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>60</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -958,10 +1032,10 @@
         <v>9.99</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -972,7 +1046,7 @@
         <v>13</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="2"/>
@@ -980,44 +1054,44 @@
     </row>
     <row r="10" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="15" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C10" s="5">
         <v>3</v>
       </c>
       <c r="D10" s="17">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="E10" s="17">
         <f t="shared" si="0"/>
-        <v>3.24</v>
+        <v>1.41</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>52</v>
+        <v>25</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="19" t="s">
-        <v>57</v>
+      <c r="B11" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="C11" s="7">
         <v>3</v>
@@ -1030,22 +1104,22 @@
         <v>4.17</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="L11" s="9"/>
       <c r="N11" s="2"/>
@@ -1054,11 +1128,11 @@
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
       <c r="D12" s="16" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E12" s="12">
         <f>SUM(E4:E11)</f>
-        <v>26.376000000000005</v>
+        <v>21.461999999999996</v>
       </c>
       <c r="L12" s="4"/>
       <c r="N12" s="2"/>
@@ -1154,8 +1228,9 @@
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" xr:uid="{71F92B68-5AF9-4964-86D1-EF1E596E8255}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{120700BC-C273-4E2A-9F63-48B560E5AE8A}"/>
+    <hyperlink ref="H7" r:id="rId3" xr:uid="{AFA1F6F5-3880-450D-9567-B84C07781CA7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId3"/>
+  <pageSetup orientation="landscape" r:id="rId4"/>
 </worksheet>
 </file>